--- a/dev_docs/Tetra数值表_26_5_21.xlsx
+++ b/dev_docs/Tetra数值表_26_5_21.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\SDBF\dev_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831CEFBD-1D61-4940-9092-A1E8D81E616E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18431BB-4EC1-49C7-BC26-1FDD316615C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33144" yWindow="-5508" windowWidth="26436" windowHeight="15432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="476">
   <si>
     <t>刀刃</t>
   </si>
@@ -1133,17 +1133,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>阶段</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>发狂抵抗+5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>'kubejs:scoria_ingot'</t>
-  </si>
-  <si>
     <t>熔渣锭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1171,12 +1164,6 @@
   <si>
     <t>幽光</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>'midnight:rendium_shard'</t>
-  </si>
-  <si>
-    <t>铼碎片</t>
   </si>
   <si>
     <t>软</t>
@@ -1216,10 +1203,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>冰霜伤害+14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>'#forge:ingots/manasteel'</t>
   </si>
   <si>
@@ -1828,10 +1811,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>生命值-4%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>护甲穿透+</t>
     </r>
@@ -2035,11 +2014,85 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>暴击伤害+0.08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击-1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻伤害+16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻伤害+14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'kubejs:alpha_dust'</t>
+  </si>
+  <si>
+    <t>'kubejs:ml_computing_ingot'</t>
+  </si>
+  <si>
+    <t>'kubejs:anchor_shard'</t>
+  </si>
+  <si>
+    <t>'kubejs:basepoint_alloy'</t>
+  </si>
+  <si>
+    <t>'kubejs:chaotic_truth'</t>
+  </si>
+  <si>
+    <t>'kubejs:radiation_components'</t>
+  </si>
+  <si>
+    <t>'kubejs:silica_rich_asteroid_rock'</t>
+  </si>
+  <si>
+    <t>'kubejs:bizarre_matter_dust'</t>
+  </si>
+  <si>
+    <t>'cataclysm:lacrima'</t>
+  </si>
+  <si>
+    <t>'the_bumblezone:glistering_honey_crystal'</t>
+  </si>
+  <si>
+    <t>'the_bumblezone:redstone_honey_web'</t>
+  </si>
+  <si>
+    <t>'kubejs:delta_dust'</t>
+  </si>
+  <si>
+    <t>'cataclysm:essence_of_the_storm'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/terrasteel'</t>
+  </si>
+  <si>
+    <t>'#the_bumblezone:ancient_wax/full_blocks'</t>
+  </si>
+  <si>
+    <t>'kubejs:galatic_cycle_component'</t>
+  </si>
+  <si>
+    <t>'the_bumblezone:royal_jelly_bottle'</t>
+  </si>
+  <si>
+    <t>'kubejs:multifaceted_ambrosia'</t>
+  </si>
+  <si>
+    <t>其他特性</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值-2%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2611,10 +2664,10 @@
         <v>4</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>5</v>
@@ -2635,7 +2688,7 @@
         <v>10</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>269</v>
@@ -2692,7 +2745,7 @@
         <v>14</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="U2" s="30" t="s">
         <v>274</v>
@@ -2748,7 +2801,7 @@
         <v>20</v>
       </c>
       <c r="U3" s="30" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="V3" s="31"/>
       <c r="W3" s="31"/>
@@ -2814,7 +2867,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>27</v>
@@ -2881,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="P7" s="24" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="Q7" s="24" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="R7" s="24" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2901,7 +2954,7 @@
         <v>14</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2917,8 +2970,8 @@
       <c r="I9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>329</v>
+      <c r="W9" s="3" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2980,9 +3033,9 @@
         <v>45</v>
       </c>
       <c r="T10" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="U10" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="W10" s="3" t="s">
         <v>289</v>
       </c>
     </row>
@@ -3603,7 +3656,7 @@
         <v>2</v>
       </c>
       <c r="Q21" s="23" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
@@ -3876,7 +3929,7 @@
         <v>91</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="S26" s="9"/>
       <c r="U26" s="24"/>
@@ -4099,7 +4152,7 @@
         <v>99</v>
       </c>
       <c r="R30" s="23" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="S30" s="9"/>
       <c r="U30" s="24"/>
@@ -4154,7 +4207,7 @@
         <v>86</v>
       </c>
       <c r="R31" s="23" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="S31" s="9"/>
       <c r="U31" s="24"/>
@@ -4322,7 +4375,7 @@
         <v>5</v>
       </c>
       <c r="Q34" s="23" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
@@ -4386,7 +4439,7 @@
         <v>113</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="S35" s="9"/>
       <c r="U35" s="24"/>
@@ -4662,7 +4715,7 @@
         <v>4</v>
       </c>
       <c r="Q40" s="23" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
@@ -4780,7 +4833,7 @@
         <v>113</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="S42" s="9"/>
       <c r="U42" s="24"/>
@@ -4894,7 +4947,7 @@
         <v>4</v>
       </c>
       <c r="Q44" s="23" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
@@ -5117,7 +5170,7 @@
         <v>4</v>
       </c>
       <c r="Q48" s="23" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="R48" s="9"/>
       <c r="S48" s="9"/>
@@ -5458,7 +5511,7 @@
         <v>5</v>
       </c>
       <c r="Q54" s="23" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="R54" s="9"/>
       <c r="S54" s="9"/>
@@ -5626,7 +5679,7 @@
         <v>179</v>
       </c>
       <c r="R57" s="23" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="S57" s="9"/>
     </row>
@@ -5691,7 +5744,7 @@
         <v>183</v>
       </c>
       <c r="S58" s="23" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="U58" s="24"/>
     </row>
@@ -5986,10 +6039,10 @@
         <v>143</v>
       </c>
       <c r="R63" s="23" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="S63" s="23" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="U63" s="24"/>
     </row>
@@ -6213,7 +6266,7 @@
         <v>208</v>
       </c>
       <c r="R67" s="23" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="S67" s="9"/>
       <c r="U67" s="24"/>
@@ -6399,10 +6452,10 @@
         <v>220</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>53</v>
@@ -6443,13 +6496,13 @@
         <v>6</v>
       </c>
       <c r="Q71" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="R71" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="S71" s="23" t="s">
         <v>323</v>
-      </c>
-      <c r="R71" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="S71" s="23" t="s">
-        <v>328</v>
       </c>
       <c r="U71" s="24"/>
     </row>
@@ -6502,7 +6555,7 @@
         <v>5</v>
       </c>
       <c r="Q72" s="23" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="R72" s="9" t="s">
         <v>173</v>
@@ -6511,7 +6564,7 @@
         <v>215</v>
       </c>
       <c r="T72" s="24" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="U72" s="24"/>
     </row>
@@ -6570,10 +6623,10 @@
         <v>5</v>
       </c>
       <c r="Q73" s="23" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="R73" s="23" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="S73" s="9"/>
       <c r="U73" s="24"/>
@@ -6627,7 +6680,7 @@
         <v>7</v>
       </c>
       <c r="Q74" s="23" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="R74" s="23" t="s">
         <v>275</v>
@@ -6639,10 +6692,10 @@
         <v>226</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>53</v>
@@ -6686,7 +6739,7 @@
         <v>205</v>
       </c>
       <c r="R75" s="23" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="S75" s="9"/>
       <c r="U75" s="24"/>
@@ -6696,13 +6749,13 @@
         <v>226</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G76" s="12">
         <v>9.5</v>
@@ -6740,10 +6793,10 @@
         <v>5</v>
       </c>
       <c r="Q76" s="23" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="R76" s="23" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="S76" s="9"/>
       <c r="U76" s="24"/>
@@ -6759,7 +6812,7 @@
         <v>229</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>231</v>
@@ -6803,7 +6856,7 @@
         <v>7</v>
       </c>
       <c r="Q77" s="23" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="R77" s="9"/>
       <c r="S77" s="9"/>
@@ -6870,10 +6923,10 @@
         <v>229</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>53</v>
@@ -6914,7 +6967,7 @@
         <v>6</v>
       </c>
       <c r="Q79" s="23" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="R79" s="23"/>
       <c r="S79" s="9"/>
@@ -6969,7 +7022,7 @@
         <v>10</v>
       </c>
       <c r="Q80" s="23" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="R80" s="9"/>
       <c r="S80" s="9"/>
@@ -6980,10 +7033,10 @@
         <v>229</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>294</v>
@@ -7040,13 +7093,13 @@
         <v>65</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>294</v>
@@ -7096,13 +7149,13 @@
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="12" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>294</v>
@@ -7152,13 +7205,13 @@
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C84" s="12" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>294</v>
@@ -7211,7 +7264,7 @@
         <v>297</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E85" s="12" t="s">
         <v>298</v>
@@ -7255,10 +7308,10 @@
         <v>8</v>
       </c>
       <c r="Q85" s="23" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="R85" s="23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="S85" s="9"/>
       <c r="U85" s="24"/>
@@ -7268,10 +7321,10 @@
         <v>297</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="F86" s="12" t="s">
         <v>294</v>
@@ -7312,10 +7365,10 @@
         <v>6</v>
       </c>
       <c r="Q86" s="23" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="R86" s="23" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="S86" s="9"/>
       <c r="U86" s="24"/>
@@ -7325,10 +7378,10 @@
         <v>297</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>294</v>
@@ -7375,19 +7428,19 @@
         <v>284</v>
       </c>
       <c r="S87" s="23" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="U87" s="24"/>
     </row>
     <row r="88" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="12" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F88" s="12" t="s">
         <v>294</v>
@@ -7428,7 +7481,7 @@
         <v>4</v>
       </c>
       <c r="Q88" s="23" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R88" s="23"/>
       <c r="S88" s="23"/>
@@ -7498,7 +7551,7 @@
         <v>215</v>
       </c>
       <c r="T89" s="24" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="U89" s="24"/>
     </row>
@@ -7632,7 +7685,7 @@
         <v>241</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F92" s="12" t="s">
         <v>53</v>
@@ -7676,7 +7729,7 @@
         <v>242</v>
       </c>
       <c r="R92" s="23" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="S92" s="23" t="s">
         <v>283</v>
@@ -7685,7 +7738,7 @@
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C93" s="12" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>218</v>
@@ -7732,13 +7785,13 @@
         <v>6</v>
       </c>
       <c r="Q93" s="23" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="R93" s="23" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="S93" s="23" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="U93" s="24"/>
     </row>
@@ -7794,10 +7847,10 @@
         <v>286</v>
       </c>
       <c r="R94" s="23" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="S94" s="23" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="U94" s="24"/>
     </row>
@@ -7859,10 +7912,10 @@
         <v>287</v>
       </c>
       <c r="R95" s="23" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="S95" s="23" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="U95" s="24"/>
     </row>
@@ -7924,17 +7977,17 @@
         <v>253</v>
       </c>
       <c r="R96" s="23" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="S96" s="9" t="s">
         <v>254</v>
       </c>
       <c r="T96" s="24" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="U96" s="24"/>
     </row>
-    <row r="97" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C97" s="12" t="s">
         <v>250</v>
       </c>
@@ -7986,37 +8039,39 @@
         <v>147</v>
       </c>
       <c r="R97" s="23" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="S97" s="23" t="s">
         <v>288</v>
       </c>
       <c r="U97" s="24"/>
     </row>
-    <row r="98" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>395</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="D98" s="23"/>
-      <c r="E98" s="23" t="s">
-        <v>396</v>
-      </c>
-      <c r="F98" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="F98" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G98" s="9">
+      <c r="G98" s="5">
         <v>28</v>
       </c>
-      <c r="H98" s="9">
+      <c r="H98" s="5">
         <v>12</v>
       </c>
-      <c r="I98" s="9">
+      <c r="I98" s="5">
         <v>15</v>
       </c>
       <c r="J98" s="17">
@@ -8046,40 +8101,43 @@
         <v>6</v>
       </c>
       <c r="Q98" s="23" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="R98" s="23" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="S98" s="23"/>
       <c r="T98" s="23" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="99" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+      <c r="W98" s="24"/>
+    </row>
+    <row r="99" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>105</v>
       </c>
       <c r="B99" s="3">
         <v>125</v>
       </c>
-      <c r="C99" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="D99" s="23"/>
-      <c r="E99" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="F99" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="G99" s="9">
+      <c r="C99" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="G99" s="12">
         <v>32</v>
       </c>
-      <c r="H99" s="9">
+      <c r="H99" s="12">
         <v>25</v>
       </c>
-      <c r="I99" s="9">
+      <c r="I99" s="12">
         <v>20</v>
       </c>
       <c r="J99" s="17">
@@ -8109,34 +8167,37 @@
         <v>8</v>
       </c>
       <c r="Q99" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="R99" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="S99" s="23"/>
       <c r="T99" s="23" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="100" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C100" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="D100" s="23"/>
-      <c r="E100" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F100" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="W99" s="24"/>
+    </row>
+    <row r="100" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C100" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="F100" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G100" s="9">
+      <c r="G100" s="12">
         <v>30</v>
       </c>
-      <c r="H100" s="9">
+      <c r="H100" s="12">
         <v>30</v>
       </c>
-      <c r="I100" s="9">
+      <c r="I100" s="12">
         <v>20</v>
       </c>
       <c r="J100" s="17">
@@ -8166,34 +8227,37 @@
         <v>9</v>
       </c>
       <c r="Q100" s="23" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="R100" s="23" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="S100" s="23"/>
       <c r="T100" s="23" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="101" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C101" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="D101" s="23"/>
-      <c r="E101" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="F101" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="W100" s="24"/>
+    </row>
+    <row r="101" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C101" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="F101" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G101" s="9">
+      <c r="G101" s="12">
         <v>30</v>
       </c>
-      <c r="H101" s="9">
+      <c r="H101" s="12">
         <v>32</v>
       </c>
-      <c r="I101" s="9">
+      <c r="I101" s="12">
         <v>19</v>
       </c>
       <c r="J101" s="17">
@@ -8223,32 +8287,35 @@
         <v>7</v>
       </c>
       <c r="Q101" s="23" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="R101" s="23" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="S101" s="23"/>
       <c r="T101" s="23"/>
-    </row>
-    <row r="102" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C102" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="D102" s="23"/>
-      <c r="E102" s="23" t="s">
-        <v>421</v>
-      </c>
-      <c r="F102" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="G102" s="9">
+      <c r="W101" s="24"/>
+    </row>
+    <row r="102" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C102" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="G102" s="12">
         <v>26</v>
       </c>
-      <c r="H102" s="9">
+      <c r="H102" s="12">
         <v>35</v>
       </c>
-      <c r="I102" s="9">
+      <c r="I102" s="12">
         <v>20</v>
       </c>
       <c r="J102" s="17">
@@ -8278,40 +8345,43 @@
         <v>7</v>
       </c>
       <c r="Q102" s="23" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="R102" s="23" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="S102" s="23" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="T102" s="23"/>
-    </row>
-    <row r="103" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W102" s="24"/>
+    </row>
+    <row r="103" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>120</v>
       </c>
       <c r="B103" s="3">
         <v>140</v>
       </c>
-      <c r="C103" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="D103" s="23"/>
-      <c r="E103" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="F103" s="23" t="s">
+      <c r="C103" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F103" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G103" s="9">
+      <c r="G103" s="5">
         <v>36</v>
       </c>
-      <c r="H103" s="9">
+      <c r="H103" s="5">
         <v>30</v>
       </c>
-      <c r="I103" s="9">
+      <c r="I103" s="5">
         <v>22.5</v>
       </c>
       <c r="J103" s="17">
@@ -8341,34 +8411,37 @@
         <v>9</v>
       </c>
       <c r="Q103" s="23" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="R103" s="23" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="S103" s="23"/>
       <c r="T103" s="23" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="104" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="D104" s="23"/>
-      <c r="E104" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="F104" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="G104" s="9">
+        <v>404</v>
+      </c>
+      <c r="W103" s="24"/>
+    </row>
+    <row r="104" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C104" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G104" s="5">
         <v>35</v>
       </c>
-      <c r="H104" s="9">
+      <c r="H104" s="5">
         <v>26</v>
       </c>
-      <c r="I104" s="9">
+      <c r="I104" s="5">
         <v>22</v>
       </c>
       <c r="J104" s="17">
@@ -8398,34 +8471,37 @@
         <v>10</v>
       </c>
       <c r="Q104" s="23" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="R104" s="23" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="S104" s="23" t="s">
-        <v>418</v>
+        <v>475</v>
       </c>
       <c r="T104" s="24"/>
-    </row>
-    <row r="105" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C105" s="23" t="s">
-        <v>402</v>
-      </c>
-      <c r="D105" s="23"/>
-      <c r="E105" s="23" t="s">
-        <v>403</v>
-      </c>
-      <c r="F105" s="23" t="s">
+      <c r="W104" s="24"/>
+    </row>
+    <row r="105" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C105" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="F105" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G105" s="9">
+      <c r="G105" s="5">
         <v>38</v>
       </c>
-      <c r="H105" s="9">
+      <c r="H105" s="5">
         <v>24</v>
       </c>
-      <c r="I105" s="9">
+      <c r="I105" s="5">
         <v>23</v>
       </c>
       <c r="J105" s="17">
@@ -8455,48 +8531,51 @@
         <v>13</v>
       </c>
       <c r="Q105" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="R105" s="23" t="s">
-        <v>435</v>
+        <v>421</v>
+      </c>
+      <c r="R105" s="24" t="s">
+        <v>429</v>
       </c>
       <c r="S105" s="23" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="T105" s="24" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="U105" s="24" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="V105" s="24" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="106" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+      <c r="W105" s="24"/>
+    </row>
+    <row r="106" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>135</v>
       </c>
       <c r="B106" s="3">
         <v>155</v>
       </c>
-      <c r="C106" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="D106" s="9"/>
-      <c r="E106" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="F106" s="23" t="s">
+      <c r="C106" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="F106" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G106" s="9">
+      <c r="G106" s="12">
         <v>39</v>
       </c>
-      <c r="H106" s="9">
+      <c r="H106" s="12">
         <v>24</v>
       </c>
-      <c r="I106" s="9">
+      <c r="I106" s="12">
         <v>24</v>
       </c>
       <c r="J106" s="17">
@@ -8529,36 +8608,39 @@
         <v>242</v>
       </c>
       <c r="R106" s="24" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="S106" s="23" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="107" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>388</v>
+      </c>
+      <c r="W106" s="24"/>
+    </row>
+    <row r="107" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>165</v>
       </c>
       <c r="B107" s="3">
         <v>180</v>
       </c>
-      <c r="C107" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="D107" s="23"/>
-      <c r="E107" s="23" t="s">
-        <v>387</v>
-      </c>
-      <c r="F107" s="23" t="s">
+      <c r="C107" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="F107" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G107" s="9">
+      <c r="G107" s="5">
         <v>52</v>
       </c>
-      <c r="H107" s="9">
+      <c r="H107" s="5">
         <v>35</v>
       </c>
-      <c r="I107" s="9">
+      <c r="I107" s="5">
         <v>29</v>
       </c>
       <c r="J107" s="17">
@@ -8588,36 +8670,41 @@
         <v>16</v>
       </c>
       <c r="Q107" s="23" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="R107" s="23" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="S107" s="9" t="s">
         <v>242</v>
       </c>
       <c r="T107" s="24" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="108" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C108" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="D108" s="23"/>
-      <c r="E108" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="F108" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="G108" s="9">
+        <v>335</v>
+      </c>
+      <c r="W107" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C108" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G108" s="5">
         <v>46</v>
       </c>
-      <c r="H108" s="9">
+      <c r="H108" s="5">
         <v>50</v>
       </c>
-      <c r="I108" s="9">
+      <c r="I108" s="5">
         <v>29</v>
       </c>
       <c r="J108" s="17">
@@ -8647,36 +8734,45 @@
         <v>8</v>
       </c>
       <c r="Q108" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="R108" s="23"/>
-      <c r="S108" s="9"/>
+        <v>431</v>
+      </c>
+      <c r="R108" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="S108" s="23" t="s">
+        <v>422</v>
+      </c>
       <c r="T108" s="24"/>
-    </row>
-    <row r="109" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W108" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>180</v>
       </c>
       <c r="B109" s="3">
         <v>190</v>
       </c>
-      <c r="C109" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="D109" s="9"/>
-      <c r="E109" s="23" t="s">
-        <v>424</v>
-      </c>
-      <c r="F109" s="23" t="s">
+      <c r="C109" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="F109" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G109" s="9">
+      <c r="G109" s="12">
         <v>52</v>
       </c>
-      <c r="H109" s="9">
+      <c r="H109" s="12">
         <v>50</v>
       </c>
-      <c r="I109" s="9">
+      <c r="I109" s="12">
         <v>30.5</v>
       </c>
       <c r="J109" s="17">
@@ -8709,36 +8805,41 @@
         <v>276</v>
       </c>
       <c r="R109" s="23" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="S109" s="23" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="110" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+      <c r="W109" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>190</v>
       </c>
       <c r="B110" s="3">
         <v>190</v>
       </c>
-      <c r="C110" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="D110" s="9"/>
-      <c r="E110" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="F110" s="23" t="s">
+      <c r="C110" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="F110" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G110" s="9">
+      <c r="G110" s="5">
         <v>58</v>
       </c>
-      <c r="H110" s="9">
+      <c r="H110" s="5">
         <v>45</v>
       </c>
-      <c r="I110" s="9">
+      <c r="I110" s="5">
         <v>31</v>
       </c>
       <c r="J110" s="17">
@@ -8768,39 +8869,44 @@
         <v>12</v>
       </c>
       <c r="Q110" s="23" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="R110" s="23" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="S110" s="23" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="111" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>442</v>
+      </c>
+      <c r="W110" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>210</v>
       </c>
       <c r="B111" s="3">
         <v>205</v>
       </c>
-      <c r="C111" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="D111" s="9"/>
-      <c r="E111" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="F111" s="23" t="s">
+      <c r="C111" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="F111" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G111" s="9">
+      <c r="G111" s="12">
         <v>64</v>
       </c>
-      <c r="H111" s="9">
+      <c r="H111" s="12">
         <v>50</v>
       </c>
-      <c r="I111" s="9">
+      <c r="I111" s="12">
         <v>33</v>
       </c>
       <c r="J111" s="17">
@@ -8830,40 +8936,45 @@
         <v>14</v>
       </c>
       <c r="Q111" s="23" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="R111" s="23" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="S111" s="23" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="112" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>444</v>
+      </c>
+      <c r="W111" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>230</v>
       </c>
       <c r="B112" s="3">
         <v>210</v>
       </c>
-      <c r="C112" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="D112" s="9"/>
-      <c r="E112" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="F112" s="23" t="s">
+      <c r="C112" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F112" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112" s="5">
         <v>68</v>
       </c>
-      <c r="H112" s="9">
+      <c r="H112" s="5">
         <v>60</v>
       </c>
-      <c r="I112" s="9">
-        <v>34</v>
+      <c r="I112" s="5">
+        <v>32</v>
       </c>
       <c r="J112" s="17">
         <f t="shared" si="68"/>
@@ -8879,11 +8990,11 @@
       </c>
       <c r="M112" s="11">
         <f t="shared" si="51"/>
-        <v>212.5</v>
+        <v>200</v>
       </c>
       <c r="N112" s="11">
         <f t="shared" si="52"/>
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="O112" s="9">
         <v>8</v>
@@ -8892,36 +9003,41 @@
         <v>14</v>
       </c>
       <c r="Q112" s="23" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="R112" s="23" t="s">
         <v>276</v>
       </c>
       <c r="S112" s="23" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="T112" s="23" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="113" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C113" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="D113" s="9"/>
-      <c r="E113" s="23" t="s">
-        <v>441</v>
-      </c>
-      <c r="F113" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="W112" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C113" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F113" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G113" s="9">
+      <c r="G113" s="5">
         <v>74</v>
       </c>
-      <c r="H113" s="9">
+      <c r="H113" s="5">
         <v>45</v>
       </c>
-      <c r="I113" s="9">
+      <c r="I113" s="5">
         <v>34</v>
       </c>
       <c r="J113" s="17">
@@ -8951,36 +9067,41 @@
         <v>12</v>
       </c>
       <c r="Q113" s="23" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="R113" s="23" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="S113" s="24" t="s">
         <v>296</v>
       </c>
       <c r="T113" s="24" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="D114" s="9"/>
-      <c r="E114" s="23" t="s">
-        <v>442</v>
-      </c>
-      <c r="F114" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="W113" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C114" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F114" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G114" s="9">
+      <c r="G114" s="5">
         <v>64</v>
       </c>
-      <c r="H114" s="9">
+      <c r="H114" s="5">
         <v>72</v>
       </c>
-      <c r="I114" s="9">
+      <c r="I114" s="5">
         <v>34</v>
       </c>
       <c r="J114" s="17">
@@ -9010,39 +9131,44 @@
         <v>16</v>
       </c>
       <c r="Q114" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="R114" s="23" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="S114" s="23" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+      <c r="W114" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>250</v>
       </c>
       <c r="B115" s="3">
         <v>215</v>
       </c>
-      <c r="C115" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="D115" s="9"/>
-      <c r="E115" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="F115" s="23" t="s">
+      <c r="C115" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="F115" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G115" s="9">
+      <c r="G115" s="12">
         <v>78</v>
       </c>
-      <c r="H115" s="9">
+      <c r="H115" s="12">
         <v>57</v>
       </c>
-      <c r="I115" s="9">
+      <c r="I115" s="12">
         <v>35</v>
       </c>
       <c r="J115" s="17">
@@ -9072,16 +9198,19 @@
         <v>16</v>
       </c>
       <c r="Q115" s="23" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="R115" s="23" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="S115" s="23" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>444</v>
+      </c>
+      <c r="W115" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -9115,7 +9244,7 @@
       <c r="R116" s="9"/>
       <c r="S116" s="9"/>
     </row>
-    <row r="117" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -9149,7 +9278,7 @@
       <c r="R117" s="9"/>
       <c r="S117" s="9"/>
     </row>
-    <row r="118" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -9183,7 +9312,7 @@
       <c r="R118" s="9"/>
       <c r="S118" s="9"/>
     </row>
-    <row r="119" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -9217,7 +9346,7 @@
       <c r="R119" s="9"/>
       <c r="S119" s="9"/>
     </row>
-    <row r="120" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -9251,7 +9380,7 @@
       <c r="R120" s="9"/>
       <c r="S120" s="9"/>
     </row>
-    <row r="121" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -9285,7 +9414,7 @@
       <c r="R121" s="9"/>
       <c r="S121" s="9"/>
     </row>
-    <row r="122" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -9319,7 +9448,7 @@
       <c r="R122" s="9"/>
       <c r="S122" s="9"/>
     </row>
-    <row r="123" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
@@ -9353,7 +9482,7 @@
       <c r="R123" s="9"/>
       <c r="S123" s="9"/>
     </row>
-    <row r="124" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
@@ -9387,7 +9516,7 @@
       <c r="R124" s="9"/>
       <c r="S124" s="9"/>
     </row>
-    <row r="125" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
@@ -9421,7 +9550,7 @@
       <c r="R125" s="9"/>
       <c r="S125" s="9"/>
     </row>
-    <row r="126" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
@@ -9455,7 +9584,7 @@
       <c r="R126" s="9"/>
       <c r="S126" s="9"/>
     </row>
-    <row r="127" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
@@ -9489,7 +9618,7 @@
       <c r="R127" s="9"/>
       <c r="S127" s="9"/>
     </row>
-    <row r="128" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
@@ -10767,249 +10896,328 @@
       <c r="J1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="24" t="s">
-        <v>304</v>
+      <c r="K1" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>293</v>
+        <v>471</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="C2" s="5">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="D2" s="5">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E2" s="5">
-        <v>2.9</v>
+        <v>29</v>
       </c>
       <c r="F2" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="9">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>295</v>
+        <v>430</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
+        <v>413</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="L2" s="11"/>
       <c r="U2" s="24"/>
     </row>
     <row r="3" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>310</v>
+        <v>472</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>417</v>
       </c>
       <c r="C3" s="5">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D3" s="5">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E3" s="5">
+        <v>29</v>
+      </c>
+      <c r="F3" s="9">
+        <v>6</v>
+      </c>
+      <c r="G3" s="9">
         <v>8</v>
       </c>
-      <c r="F3" s="9">
-        <v>3</v>
-      </c>
-      <c r="G3" s="9">
-        <v>5</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="H3" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="K3" s="24"/>
+      <c r="L3" s="11"/>
       <c r="U3" s="24"/>
     </row>
     <row r="4" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="C4" s="5">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5">
-        <v>18</v>
-      </c>
-      <c r="E4" s="5">
-        <v>9</v>
+      <c r="A4" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C4" s="12">
+        <v>52</v>
+      </c>
+      <c r="D4" s="12">
+        <v>50</v>
+      </c>
+      <c r="E4" s="12">
+        <v>30.5</v>
       </c>
       <c r="F4" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" s="9">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
+        <v>276</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="L4" s="11"/>
       <c r="U4" s="24"/>
     </row>
     <row r="5" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="C5" s="12">
-        <v>21</v>
-      </c>
-      <c r="D5" s="12">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="A5" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" s="5">
+        <v>58</v>
+      </c>
+      <c r="D5" s="5">
+        <v>45</v>
+      </c>
+      <c r="E5" s="5">
+        <v>31</v>
+      </c>
+      <c r="F5" s="9">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9">
+        <v>12</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="L5" s="11"/>
+      <c r="U5" s="24"/>
+    </row>
+    <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="12">
+        <v>64</v>
+      </c>
+      <c r="D6" s="12">
+        <v>50</v>
+      </c>
+      <c r="E6" s="12">
+        <v>33</v>
+      </c>
+      <c r="F6" s="9">
+        <v>8</v>
+      </c>
+      <c r="G6" s="9">
+        <v>14</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="L6" s="11"/>
+      <c r="U6" s="24"/>
+    </row>
+    <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="C7" s="5">
+        <v>68</v>
+      </c>
+      <c r="D7" s="5">
+        <v>60</v>
+      </c>
+      <c r="E7" s="5">
+        <v>32</v>
+      </c>
+      <c r="F7" s="9">
+        <v>8</v>
+      </c>
+      <c r="G7" s="9">
+        <v>14</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>453</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="L7" s="11"/>
+      <c r="U7" s="24"/>
+    </row>
+    <row r="8" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C8" s="5">
+        <v>74</v>
+      </c>
+      <c r="D8" s="5">
+        <v>45</v>
+      </c>
+      <c r="E8" s="5">
+        <v>34</v>
+      </c>
+      <c r="F8" s="9">
+        <v>8</v>
+      </c>
+      <c r="G8" s="9">
+        <v>12</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C9" s="5">
+        <v>64</v>
+      </c>
+      <c r="D9" s="5">
+        <v>72</v>
+      </c>
+      <c r="E9" s="5">
+        <v>34</v>
+      </c>
+      <c r="F9" s="9">
         <v>10</v>
       </c>
-      <c r="F5" s="9">
-        <v>3</v>
-      </c>
-      <c r="G5" s="9">
-        <v>6</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="U5" s="24"/>
-    </row>
-    <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="C6" s="5">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5">
-        <v>10</v>
-      </c>
-      <c r="F6" s="9">
-        <v>4</v>
-      </c>
-      <c r="G6" s="9">
-        <v>6</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="U6" s="24"/>
-    </row>
-    <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="C7" s="12">
-        <v>14</v>
-      </c>
-      <c r="D7" s="12">
-        <v>37</v>
-      </c>
-      <c r="E7" s="12">
-        <v>11</v>
-      </c>
-      <c r="F7" s="9">
-        <v>4</v>
-      </c>
-      <c r="G7" s="9">
-        <v>4</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="U7" s="24"/>
-    </row>
-    <row r="8" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-    </row>
-    <row r="9" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
+      <c r="G9" s="9">
+        <v>16</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>447</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>448</v>
+      </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="A10" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C10" s="12">
+        <v>78</v>
+      </c>
+      <c r="D10" s="12">
+        <v>57</v>
+      </c>
+      <c r="E10" s="12">
+        <v>35</v>
+      </c>
+      <c r="F10" s="9">
+        <v>8</v>
+      </c>
+      <c r="G10" s="9">
+        <v>16</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>444</v>
+      </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
     </row>

--- a/dev_docs/Tetra数值表_26_5_21.xlsx
+++ b/dev_docs/Tetra数值表_26_5_21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18431BB-4EC1-49C7-BC26-1FDD316615C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355C9394-C1FF-44D4-91E7-B9AD8E6E030D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="555" yWindow="4350" windowWidth="26430" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="474">
   <si>
     <t>刀刃</t>
   </si>
@@ -1695,23 +1695,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1.3</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>泰拉钢</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2030,10 +2013,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>'kubejs:alpha_dust'</t>
   </si>
   <si>
@@ -2071,9 +2050,6 @@
   </si>
   <si>
     <t>'cataclysm:essence_of_the_storm'</t>
-  </si>
-  <si>
-    <t>'#forge:ingots/terrasteel'</t>
   </si>
   <si>
     <t>'#the_bumblezone:ancient_wax/full_blocks'</t>
@@ -2093,6 +2069,10 @@
   </si>
   <si>
     <t>生命值-2%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'#forge:ingots/terrasteel'</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2867,7 +2847,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>27</v>
@@ -2934,13 +2914,13 @@
         <v>0</v>
       </c>
       <c r="P7" s="24" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q7" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="R7" s="24" t="s">
         <v>424</v>
-      </c>
-      <c r="R7" s="24" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2954,7 +2934,7 @@
         <v>14</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5679,7 +5659,7 @@
         <v>179</v>
       </c>
       <c r="R57" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="S57" s="9"/>
     </row>
@@ -6555,7 +6535,7 @@
         <v>5</v>
       </c>
       <c r="Q72" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="R72" s="9" t="s">
         <v>173</v>
@@ -6714,7 +6694,7 @@
         <v>29.5</v>
       </c>
       <c r="K75" s="9">
-        <f t="shared" ref="K75:K106" si="41">(G75*$I$4)+(H75*$I$5)+(I75*$I$7)</f>
+        <f t="shared" ref="K75:K105" si="41">(G75*$I$4)+(H75*$I$5)+(I75*$I$7)</f>
         <v>10</v>
       </c>
       <c r="L75" s="10">
@@ -7308,7 +7288,7 @@
         <v>8</v>
       </c>
       <c r="Q85" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="R85" s="23" t="s">
         <v>304</v>
@@ -7729,7 +7709,7 @@
         <v>242</v>
       </c>
       <c r="R92" s="23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="S92" s="23" t="s">
         <v>283</v>
@@ -7788,7 +7768,7 @@
         <v>350</v>
       </c>
       <c r="R93" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="S93" s="23" t="s">
         <v>372</v>
@@ -8057,7 +8037,7 @@
         <v>373</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>391</v>
@@ -8108,7 +8088,7 @@
       </c>
       <c r="S98" s="23"/>
       <c r="T98" s="23" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="W98" s="24"/>
     </row>
@@ -8123,7 +8103,7 @@
         <v>376</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E99" s="12" t="s">
         <v>384</v>
@@ -8174,7 +8154,7 @@
       </c>
       <c r="S99" s="23"/>
       <c r="T99" s="23" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="W99" s="24"/>
     </row>
@@ -8183,7 +8163,7 @@
         <v>376</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E100" s="12" t="s">
         <v>386</v>
@@ -8230,11 +8210,11 @@
         <v>392</v>
       </c>
       <c r="R100" s="23" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="S100" s="23"/>
       <c r="T100" s="23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="W100" s="24"/>
     </row>
@@ -8243,10 +8223,10 @@
         <v>376</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F101" s="12" t="s">
         <v>294</v>
@@ -8287,7 +8267,7 @@
         <v>7</v>
       </c>
       <c r="Q101" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="R101" s="23" t="s">
         <v>319</v>
@@ -8301,10 +8281,10 @@
         <v>376</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F102" s="12" t="s">
         <v>313</v>
@@ -8345,13 +8325,13 @@
         <v>7</v>
       </c>
       <c r="Q102" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="R102" s="23" t="s">
         <v>422</v>
       </c>
-      <c r="R102" s="23" t="s">
-        <v>423</v>
-      </c>
       <c r="S102" s="23" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="T102" s="23"/>
       <c r="W102" s="24"/>
@@ -8367,7 +8347,7 @@
         <v>377</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>383</v>
@@ -8418,7 +8398,7 @@
       </c>
       <c r="S103" s="23"/>
       <c r="T103" s="23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="W103" s="24"/>
     </row>
@@ -8427,7 +8407,7 @@
         <v>377</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>385</v>
@@ -8471,281 +8451,277 @@
         <v>10</v>
       </c>
       <c r="Q104" s="23" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R104" s="23" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S104" s="23" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="T104" s="24"/>
       <c r="W104" s="24"/>
     </row>
     <row r="105" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C105" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="F105" s="5" t="s">
+      <c r="A105" s="3">
+        <v>135</v>
+      </c>
+      <c r="B105" s="3">
+        <v>155</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="F105" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G105" s="5">
-        <v>38</v>
-      </c>
-      <c r="H105" s="5">
+      <c r="G105" s="12">
+        <v>39</v>
+      </c>
+      <c r="H105" s="12">
         <v>24</v>
       </c>
-      <c r="I105" s="5">
-        <v>23</v>
+      <c r="I105" s="12">
+        <v>24</v>
       </c>
       <c r="J105" s="17">
-        <f t="shared" ref="J105" si="63">(G105*$I$2)+(H105*$I$3)</f>
-        <v>88</v>
+        <f t="shared" ref="J105:J127" si="63">(G105*$I$2)+(H105*$I$3)</f>
+        <v>90</v>
       </c>
       <c r="K105" s="9">
-        <f t="shared" ref="K105" si="64">(G105*$I$4)+(H105*$I$5)+(I105*$I$7)</f>
-        <v>31</v>
+        <f t="shared" si="41"/>
+        <v>31.5</v>
       </c>
       <c r="L105" s="10">
-        <f t="shared" ref="L105" si="65">J105+K105</f>
-        <v>119</v>
+        <f t="shared" ref="L105:L127" si="64">J105+K105</f>
+        <v>121.5</v>
       </c>
       <c r="M105" s="11">
-        <f t="shared" ref="M105" si="66">I105*$M$2</f>
-        <v>143.75</v>
+        <f t="shared" si="51"/>
+        <v>150</v>
       </c>
       <c r="N105" s="11">
-        <f t="shared" ref="N105" si="67">I105*$M$3</f>
-        <v>34.5</v>
+        <f t="shared" si="52"/>
+        <v>36</v>
       </c>
       <c r="O105" s="9">
         <v>7</v>
       </c>
       <c r="P105" s="9">
-        <v>13</v>
-      </c>
-      <c r="Q105" s="23" t="s">
-        <v>421</v>
+        <v>7</v>
+      </c>
+      <c r="Q105" s="9" t="s">
+        <v>242</v>
       </c>
       <c r="R105" s="24" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="S105" s="23" t="s">
-        <v>400</v>
-      </c>
-      <c r="T105" s="24" t="s">
-        <v>399</v>
-      </c>
-      <c r="U105" s="24" t="s">
-        <v>407</v>
-      </c>
-      <c r="V105" s="24" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="W105" s="24"/>
     </row>
     <row r="106" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="B106" s="3">
-        <v>155</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>470</v>
-      </c>
-      <c r="E106" s="12" t="s">
-        <v>416</v>
-      </c>
-      <c r="F106" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G106" s="12">
-        <v>39</v>
-      </c>
-      <c r="H106" s="12">
-        <v>24</v>
-      </c>
-      <c r="I106" s="12">
-        <v>24</v>
+      <c r="G106" s="5">
+        <v>52</v>
+      </c>
+      <c r="H106" s="5">
+        <v>35</v>
+      </c>
+      <c r="I106" s="5">
+        <v>29</v>
       </c>
       <c r="J106" s="17">
-        <f t="shared" ref="J106:J127" si="68">(G106*$I$2)+(H106*$I$3)</f>
-        <v>90</v>
+        <f t="shared" si="63"/>
+        <v>121.5</v>
       </c>
       <c r="K106" s="9">
-        <f t="shared" si="41"/>
-        <v>31.5</v>
+        <f t="shared" ref="K106:K140" si="65">(G106*$I$4)+(H106*$I$5)+(I106*$I$7)</f>
+        <v>43.5</v>
       </c>
       <c r="L106" s="10">
-        <f t="shared" ref="L106:L127" si="69">J106+K106</f>
-        <v>121.5</v>
+        <f t="shared" si="64"/>
+        <v>165</v>
       </c>
       <c r="M106" s="11">
         <f t="shared" si="51"/>
-        <v>150</v>
+        <v>181.25</v>
       </c>
       <c r="N106" s="11">
         <f t="shared" si="52"/>
-        <v>36</v>
+        <v>43.5</v>
       </c>
       <c r="O106" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P106" s="9">
-        <v>7</v>
-      </c>
-      <c r="Q106" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q106" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="R106" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="S106" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="R106" s="24" t="s">
-        <v>419</v>
-      </c>
-      <c r="S106" s="23" t="s">
-        <v>388</v>
+      <c r="T106" s="24" t="s">
+        <v>335</v>
       </c>
       <c r="W106" s="24"/>
     </row>
     <row r="107" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="3">
-        <v>165</v>
-      </c>
-      <c r="B107" s="3">
-        <v>180</v>
-      </c>
       <c r="C107" s="5" t="s">
         <v>378</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="G107" s="5">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H107" s="5">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I107" s="5">
         <v>29</v>
       </c>
       <c r="J107" s="17">
-        <f t="shared" si="68"/>
-        <v>121.5</v>
+        <f t="shared" ref="J107" si="66">(G107*$I$2)+(H107*$I$3)</f>
+        <v>117</v>
       </c>
       <c r="K107" s="9">
-        <f t="shared" ref="K107:K140" si="70">(G107*$I$4)+(H107*$I$5)+(I107*$I$7)</f>
+        <f t="shared" ref="K107" si="67">(G107*$I$4)+(H107*$I$5)+(I107*$I$7)</f>
+        <v>48</v>
+      </c>
+      <c r="L107" s="10">
+        <f t="shared" ref="L107" si="68">J107+K107</f>
+        <v>165</v>
+      </c>
+      <c r="M107" s="11">
+        <f t="shared" ref="M107" si="69">I107*$M$2</f>
+        <v>181.25</v>
+      </c>
+      <c r="N107" s="11">
+        <f t="shared" ref="N107" si="70">I107*$M$3</f>
         <v>43.5</v>
       </c>
-      <c r="L107" s="10">
-        <f t="shared" si="69"/>
-        <v>165</v>
-      </c>
-      <c r="M107" s="11">
-        <f t="shared" si="51"/>
-        <v>181.25</v>
-      </c>
-      <c r="N107" s="11">
-        <f t="shared" si="52"/>
-        <v>43.5</v>
-      </c>
       <c r="O107" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P107" s="9">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q107" s="23" t="s">
         <v>430</v>
       </c>
       <c r="R107" s="23" t="s">
-        <v>413</v>
-      </c>
-      <c r="S107" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="T107" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="W107" s="24" t="s">
-        <v>455</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="S107" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="T107" s="24"/>
+      <c r="W107" s="24"/>
     </row>
     <row r="108" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C108" s="5" t="s">
         <v>378</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="G108" s="5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H108" s="5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I108" s="5">
         <v>29</v>
       </c>
       <c r="J108" s="17">
-        <f t="shared" ref="J108" si="71">(G108*$I$2)+(H108*$I$3)</f>
-        <v>117</v>
+        <f>(G108*$I$2)+(H108*$I$3)</f>
+        <v>120</v>
       </c>
       <c r="K108" s="9">
-        <f t="shared" ref="K108" si="72">(G108*$I$4)+(H108*$I$5)+(I108*$I$7)</f>
-        <v>48</v>
+        <f>(G108*$I$4)+(H108*$I$5)+(I108*$I$7)</f>
+        <v>45</v>
       </c>
       <c r="L108" s="10">
-        <f t="shared" ref="L108" si="73">J108+K108</f>
+        <f>J108+K108</f>
         <v>165</v>
       </c>
       <c r="M108" s="11">
-        <f t="shared" ref="M108" si="74">I108*$M$2</f>
+        <f>I108*$M$2</f>
         <v>181.25</v>
       </c>
       <c r="N108" s="11">
-        <f t="shared" ref="N108" si="75">I108*$M$3</f>
+        <f>I108*$M$3</f>
         <v>43.5</v>
       </c>
       <c r="O108" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P108" s="9">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q108" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="R108" s="23" t="s">
-        <v>454</v>
+        <v>420</v>
+      </c>
+      <c r="R108" s="24" t="s">
+        <v>428</v>
       </c>
       <c r="S108" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="T108" s="24"/>
-      <c r="W108" s="24" t="s">
-        <v>455</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="T108" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="U108" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="V108" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="W108" s="24"/>
     </row>
     <row r="109" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
@@ -8755,13 +8731,13 @@
         <v>190</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F109" s="12" t="s">
         <v>294</v>
@@ -8776,15 +8752,15 @@
         <v>30.5</v>
       </c>
       <c r="J109" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>129</v>
       </c>
       <c r="K109" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>51</v>
       </c>
       <c r="L109" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>180</v>
       </c>
       <c r="M109" s="11">
@@ -8805,14 +8781,12 @@
         <v>276</v>
       </c>
       <c r="R109" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="S109" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="S109" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="W109" s="24" t="s">
-        <v>455</v>
-      </c>
+      <c r="W109" s="24"/>
     </row>
     <row r="110" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
@@ -8825,10 +8799,10 @@
         <v>375</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>294</v>
@@ -8843,15 +8817,15 @@
         <v>31</v>
       </c>
       <c r="J110" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>138.5</v>
       </c>
       <c r="K110" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>51.5</v>
       </c>
       <c r="L110" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>190</v>
       </c>
       <c r="M110" s="11">
@@ -8869,17 +8843,15 @@
         <v>12</v>
       </c>
       <c r="Q110" s="23" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="R110" s="23" t="s">
         <v>369</v>
       </c>
       <c r="S110" s="23" t="s">
-        <v>442</v>
-      </c>
-      <c r="W110" s="24" t="s">
-        <v>455</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="W110" s="24"/>
     </row>
     <row r="111" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
@@ -8892,10 +8864,10 @@
         <v>379</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F111" s="12" t="s">
         <v>294</v>
@@ -8910,15 +8882,15 @@
         <v>33</v>
       </c>
       <c r="J111" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>153</v>
       </c>
       <c r="K111" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>57</v>
       </c>
       <c r="L111" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>210</v>
       </c>
       <c r="M111" s="11">
@@ -8936,17 +8908,15 @@
         <v>14</v>
       </c>
       <c r="Q111" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="R111" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="S111" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="R111" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="S111" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="W111" s="24" t="s">
-        <v>455</v>
-      </c>
+      <c r="W111" s="24"/>
     </row>
     <row r="112" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
@@ -8959,10 +8929,10 @@
         <v>380</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>294</v>
@@ -8977,15 +8947,15 @@
         <v>32</v>
       </c>
       <c r="J112" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>166</v>
       </c>
       <c r="K112" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>64</v>
       </c>
       <c r="L112" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>230</v>
       </c>
       <c r="M112" s="11">
@@ -9003,30 +8973,28 @@
         <v>14</v>
       </c>
       <c r="Q112" s="23" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="R112" s="23" t="s">
         <v>276</v>
       </c>
       <c r="S112" s="23" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="T112" s="23" t="s">
-        <v>446</v>
-      </c>
-      <c r="W112" s="24" t="s">
-        <v>455</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="W112" s="24"/>
     </row>
     <row r="113" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C113" s="5" t="s">
         <v>380</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>294</v>
@@ -9041,23 +9009,23 @@
         <v>34</v>
       </c>
       <c r="J113" s="17">
-        <f t="shared" ref="J113:J114" si="76">(G113*$I$2)+(H113*$I$3)</f>
+        <f t="shared" ref="J113:J114" si="71">(G113*$I$2)+(H113*$I$3)</f>
         <v>170.5</v>
       </c>
       <c r="K113" s="9">
-        <f t="shared" ref="K113:K114" si="77">(G113*$I$4)+(H113*$I$5)+(I113*$I$7)</f>
+        <f t="shared" ref="K113:K114" si="72">(G113*$I$4)+(H113*$I$5)+(I113*$I$7)</f>
         <v>59.5</v>
       </c>
       <c r="L113" s="10">
-        <f t="shared" ref="L113:L114" si="78">J113+K113</f>
+        <f t="shared" ref="L113:L114" si="73">J113+K113</f>
         <v>230</v>
       </c>
       <c r="M113" s="11">
-        <f t="shared" ref="M113:M114" si="79">I113*$M$2</f>
+        <f t="shared" ref="M113:M114" si="74">I113*$M$2</f>
         <v>212.5</v>
       </c>
       <c r="N113" s="11">
-        <f t="shared" ref="N113:N114" si="80">I113*$M$3</f>
+        <f t="shared" ref="N113:N114" si="75">I113*$M$3</f>
         <v>51</v>
       </c>
       <c r="O113" s="9">
@@ -9067,30 +9035,28 @@
         <v>12</v>
       </c>
       <c r="Q113" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="R113" s="23" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="S113" s="24" t="s">
         <v>296</v>
       </c>
       <c r="T113" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="W113" s="24" t="s">
-        <v>455</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="W113" s="24"/>
     </row>
     <row r="114" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C114" s="5" t="s">
         <v>380</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>294</v>
@@ -9105,23 +9071,23 @@
         <v>34</v>
       </c>
       <c r="J114" s="17">
-        <f t="shared" si="76"/>
+        <f t="shared" si="71"/>
         <v>164</v>
       </c>
       <c r="K114" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="72"/>
         <v>68</v>
       </c>
       <c r="L114" s="10">
-        <f t="shared" si="78"/>
+        <f t="shared" si="73"/>
         <v>232</v>
       </c>
       <c r="M114" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="74"/>
         <v>212.5</v>
       </c>
       <c r="N114" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>51</v>
       </c>
       <c r="O114" s="9">
@@ -9131,17 +9097,15 @@
         <v>16</v>
       </c>
       <c r="Q114" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="R114" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="S114" s="23" t="s">
         <v>447</v>
       </c>
-      <c r="R114" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="S114" s="23" t="s">
-        <v>448</v>
-      </c>
-      <c r="W114" s="24" t="s">
-        <v>455</v>
-      </c>
+      <c r="W114" s="24"/>
     </row>
     <row r="115" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
@@ -9154,10 +9118,10 @@
         <v>381</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>294</v>
@@ -9172,15 +9136,15 @@
         <v>35</v>
       </c>
       <c r="J115" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>184.5</v>
       </c>
       <c r="K115" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>67.5</v>
       </c>
       <c r="L115" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>252</v>
       </c>
       <c r="M115" s="11">
@@ -9198,17 +9162,15 @@
         <v>16</v>
       </c>
       <c r="Q115" s="23" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R115" s="23" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="S115" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="W115" s="24" t="s">
-        <v>455</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="W115" s="24"/>
     </row>
     <row r="116" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C116" s="9"/>
@@ -9219,15 +9181,15 @@
       <c r="H116" s="9"/>
       <c r="I116" s="9"/>
       <c r="J116" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K116" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L116" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M116" s="11">
@@ -9253,15 +9215,15 @@
       <c r="H117" s="9"/>
       <c r="I117" s="9"/>
       <c r="J117" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K117" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L117" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M117" s="11">
@@ -9287,15 +9249,15 @@
       <c r="H118" s="9"/>
       <c r="I118" s="9"/>
       <c r="J118" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K118" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L118" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M118" s="11">
@@ -9321,15 +9283,15 @@
       <c r="H119" s="9"/>
       <c r="I119" s="9"/>
       <c r="J119" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K119" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L119" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M119" s="11">
@@ -9355,23 +9317,23 @@
       <c r="H120" s="9"/>
       <c r="I120" s="9"/>
       <c r="J120" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K120" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L120" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M120" s="11">
-        <f t="shared" ref="M120:M163" si="81">I120*$M$2</f>
+        <f t="shared" ref="M120:M163" si="76">I120*$M$2</f>
         <v>0</v>
       </c>
       <c r="N120" s="11">
-        <f t="shared" ref="N120:N163" si="82">I120*$M$3</f>
+        <f t="shared" ref="N120:N163" si="77">I120*$M$3</f>
         <v>0</v>
       </c>
       <c r="O120" s="9"/>
@@ -9389,23 +9351,23 @@
       <c r="H121" s="9"/>
       <c r="I121" s="9"/>
       <c r="J121" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K121" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L121" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M121" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N121" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O121" s="9"/>
@@ -9423,23 +9385,23 @@
       <c r="H122" s="9"/>
       <c r="I122" s="9"/>
       <c r="J122" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K122" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L122" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M122" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N122" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O122" s="9"/>
@@ -9457,23 +9419,23 @@
       <c r="H123" s="9"/>
       <c r="I123" s="9"/>
       <c r="J123" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K123" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L123" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M123" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N123" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O123" s="9"/>
@@ -9491,23 +9453,23 @@
       <c r="H124" s="9"/>
       <c r="I124" s="9"/>
       <c r="J124" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K124" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L124" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M124" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N124" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O124" s="9"/>
@@ -9525,23 +9487,23 @@
       <c r="H125" s="9"/>
       <c r="I125" s="9"/>
       <c r="J125" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K125" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L125" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M125" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N125" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O125" s="9"/>
@@ -9559,23 +9521,23 @@
       <c r="H126" s="9"/>
       <c r="I126" s="9"/>
       <c r="J126" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K126" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L126" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M126" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N126" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O126" s="9"/>
@@ -9593,23 +9555,23 @@
       <c r="H127" s="9"/>
       <c r="I127" s="9"/>
       <c r="J127" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K127" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L127" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M127" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N127" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O127" s="9"/>
@@ -9627,23 +9589,23 @@
       <c r="H128" s="9"/>
       <c r="I128" s="9"/>
       <c r="J128" s="17">
-        <f t="shared" ref="J128:J163" si="83">(G128*$I$2)+(H128*$I$3)</f>
+        <f t="shared" ref="J128:J163" si="78">(G128*$I$2)+(H128*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K128" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L128" s="10">
-        <f t="shared" ref="L128:L163" si="84">J128+K128</f>
+        <f t="shared" ref="L128:L163" si="79">J128+K128</f>
         <v>0</v>
       </c>
       <c r="M128" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N128" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O128" s="9"/>
@@ -9661,23 +9623,23 @@
       <c r="H129" s="9"/>
       <c r="I129" s="9"/>
       <c r="J129" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K129" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L129" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M129" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N129" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O129" s="9"/>
@@ -9695,23 +9657,23 @@
       <c r="H130" s="9"/>
       <c r="I130" s="9"/>
       <c r="J130" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K130" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L130" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M130" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N130" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O130" s="9"/>
@@ -9729,23 +9691,23 @@
       <c r="H131" s="9"/>
       <c r="I131" s="9"/>
       <c r="J131" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K131" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L131" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M131" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N131" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O131" s="9"/>
@@ -9763,23 +9725,23 @@
       <c r="H132" s="9"/>
       <c r="I132" s="9"/>
       <c r="J132" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K132" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L132" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M132" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N132" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O132" s="9"/>
@@ -9797,23 +9759,23 @@
       <c r="H133" s="9"/>
       <c r="I133" s="9"/>
       <c r="J133" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K133" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L133" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M133" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N133" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O133" s="9"/>
@@ -9831,23 +9793,23 @@
       <c r="H134" s="9"/>
       <c r="I134" s="9"/>
       <c r="J134" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K134" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L134" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M134" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N134" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O134" s="9"/>
@@ -9865,23 +9827,23 @@
       <c r="H135" s="9"/>
       <c r="I135" s="9"/>
       <c r="J135" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K135" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L135" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M135" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N135" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O135" s="9"/>
@@ -9899,23 +9861,23 @@
       <c r="H136" s="9"/>
       <c r="I136" s="9"/>
       <c r="J136" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K136" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L136" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M136" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N136" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O136" s="9"/>
@@ -9933,23 +9895,23 @@
       <c r="H137" s="9"/>
       <c r="I137" s="9"/>
       <c r="J137" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K137" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L137" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M137" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N137" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O137" s="9"/>
@@ -9967,23 +9929,23 @@
       <c r="H138" s="9"/>
       <c r="I138" s="9"/>
       <c r="J138" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K138" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L138" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M138" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N138" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O138" s="9"/>
@@ -10001,23 +9963,23 @@
       <c r="H139" s="9"/>
       <c r="I139" s="9"/>
       <c r="J139" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K139" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L139" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M139" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N139" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O139" s="9"/>
@@ -10035,23 +9997,23 @@
       <c r="H140" s="9"/>
       <c r="I140" s="9"/>
       <c r="J140" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K140" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L140" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M140" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N140" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O140" s="9"/>
@@ -10069,23 +10031,23 @@
       <c r="H141" s="9"/>
       <c r="I141" s="9"/>
       <c r="J141" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K141" s="9">
-        <f t="shared" ref="K141:K163" si="85">(G141*$I$4)+(H141*$I$5)+(I141*$I$7)</f>
+        <f t="shared" ref="K141:K163" si="80">(G141*$I$4)+(H141*$I$5)+(I141*$I$7)</f>
         <v>0</v>
       </c>
       <c r="L141" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M141" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N141" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O141" s="9"/>
@@ -10103,23 +10065,23 @@
       <c r="H142" s="9"/>
       <c r="I142" s="9"/>
       <c r="J142" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K142" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L142" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M142" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N142" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O142" s="9"/>
@@ -10137,23 +10099,23 @@
       <c r="H143" s="9"/>
       <c r="I143" s="9"/>
       <c r="J143" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K143" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L143" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M143" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N143" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O143" s="9"/>
@@ -10171,23 +10133,23 @@
       <c r="H144" s="9"/>
       <c r="I144" s="9"/>
       <c r="J144" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K144" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L144" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M144" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N144" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O144" s="9"/>
@@ -10205,23 +10167,23 @@
       <c r="H145" s="9"/>
       <c r="I145" s="9"/>
       <c r="J145" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K145" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L145" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M145" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N145" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O145" s="9"/>
@@ -10239,23 +10201,23 @@
       <c r="H146" s="9"/>
       <c r="I146" s="9"/>
       <c r="J146" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K146" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L146" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M146" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N146" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O146" s="9"/>
@@ -10273,23 +10235,23 @@
       <c r="H147" s="9"/>
       <c r="I147" s="9"/>
       <c r="J147" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K147" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L147" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M147" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N147" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O147" s="9"/>
@@ -10307,23 +10269,23 @@
       <c r="H148" s="9"/>
       <c r="I148" s="9"/>
       <c r="J148" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K148" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L148" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M148" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N148" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O148" s="9"/>
@@ -10341,23 +10303,23 @@
       <c r="H149" s="9"/>
       <c r="I149" s="9"/>
       <c r="J149" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K149" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L149" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M149" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N149" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O149" s="9"/>
@@ -10375,23 +10337,23 @@
       <c r="H150" s="9"/>
       <c r="I150" s="9"/>
       <c r="J150" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K150" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L150" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M150" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N150" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O150" s="9"/>
@@ -10409,23 +10371,23 @@
       <c r="H151" s="9"/>
       <c r="I151" s="9"/>
       <c r="J151" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K151" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L151" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M151" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N151" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O151" s="9"/>
@@ -10443,23 +10405,23 @@
       <c r="H152" s="9"/>
       <c r="I152" s="9"/>
       <c r="J152" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K152" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L152" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M152" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N152" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O152" s="9"/>
@@ -10477,23 +10439,23 @@
       <c r="H153" s="9"/>
       <c r="I153" s="9"/>
       <c r="J153" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K153" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L153" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M153" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N153" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O153" s="9"/>
@@ -10511,23 +10473,23 @@
       <c r="H154" s="9"/>
       <c r="I154" s="9"/>
       <c r="J154" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K154" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L154" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M154" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N154" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O154" s="9"/>
@@ -10545,23 +10507,23 @@
       <c r="H155" s="9"/>
       <c r="I155" s="9"/>
       <c r="J155" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K155" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L155" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M155" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N155" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O155" s="9"/>
@@ -10579,23 +10541,23 @@
       <c r="H156" s="9"/>
       <c r="I156" s="9"/>
       <c r="J156" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K156" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L156" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M156" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N156" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O156" s="9"/>
@@ -10613,23 +10575,23 @@
       <c r="H157" s="9"/>
       <c r="I157" s="9"/>
       <c r="J157" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K157" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L157" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M157" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N157" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O157" s="9"/>
@@ -10647,23 +10609,23 @@
       <c r="H158" s="9"/>
       <c r="I158" s="9"/>
       <c r="J158" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K158" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L158" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M158" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N158" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O158" s="9"/>
@@ -10681,23 +10643,23 @@
       <c r="H159" s="9"/>
       <c r="I159" s="9"/>
       <c r="J159" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K159" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L159" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M159" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N159" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O159" s="9"/>
@@ -10715,23 +10677,23 @@
       <c r="H160" s="9"/>
       <c r="I160" s="9"/>
       <c r="J160" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K160" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L160" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M160" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N160" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O160" s="9"/>
@@ -10749,23 +10711,23 @@
       <c r="H161" s="9"/>
       <c r="I161" s="9"/>
       <c r="J161" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K161" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L161" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M161" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N161" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O161" s="9"/>
@@ -10783,23 +10745,23 @@
       <c r="H162" s="9"/>
       <c r="I162" s="9"/>
       <c r="J162" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K162" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L162" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M162" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N162" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O162" s="9"/>
@@ -10817,23 +10779,23 @@
       <c r="H163" s="9"/>
       <c r="I163" s="9"/>
       <c r="J163" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K163" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L163" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M163" s="11">
-        <f t="shared" si="81"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N163" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O163" s="9"/>
@@ -10897,18 +10859,18 @@
         <v>45</v>
       </c>
       <c r="K1" s="28" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>382</v>
@@ -10929,10 +10891,10 @@
         <v>16</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>242</v>
@@ -10945,10 +10907,10 @@
     </row>
     <row r="3" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C3" s="5">
         <v>46</v>
@@ -10966,13 +10928,13 @@
         <v>8</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J3" s="23" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K3" s="24"/>
       <c r="L3" s="11"/>
@@ -10980,10 +10942,10 @@
     </row>
     <row r="4" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C4" s="12">
         <v>52</v>
@@ -11004,20 +10966,20 @@
         <v>276</v>
       </c>
       <c r="I4" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="J4" s="23" t="s">
         <v>439</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>440</v>
       </c>
       <c r="L4" s="11"/>
       <c r="U4" s="24"/>
     </row>
     <row r="5" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C5" s="5">
         <v>58</v>
@@ -11035,23 +10997,23 @@
         <v>12</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I5" s="23" t="s">
         <v>369</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L5" s="11"/>
       <c r="U5" s="24"/>
     </row>
     <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C6" s="12">
         <v>64</v>
@@ -11069,23 +11031,23 @@
         <v>14</v>
       </c>
       <c r="H6" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="J6" s="23" t="s">
         <v>443</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>444</v>
       </c>
       <c r="L6" s="11"/>
       <c r="U6" s="24"/>
     </row>
     <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C7" s="5">
         <v>68</v>
@@ -11103,26 +11065,26 @@
         <v>14</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I7" s="23" t="s">
         <v>276</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L7" s="11"/>
       <c r="U7" s="24"/>
     </row>
     <row r="8" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C8" s="5">
         <v>74</v>
@@ -11140,25 +11102,25 @@
         <v>12</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J8" s="24" t="s">
         <v>296</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L8" s="11"/>
     </row>
     <row r="9" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C9" s="5">
         <v>64</v>
@@ -11176,23 +11138,23 @@
         <v>16</v>
       </c>
       <c r="H9" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>447</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>448</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C10" s="12">
         <v>78</v>
@@ -11210,13 +11172,13 @@
         <v>16</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>

--- a/dev_docs/Tetra数值表_26_5_21.xlsx
+++ b/dev_docs/Tetra数值表_26_5_21.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\SDBF\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355C9394-C1FF-44D4-91E7-B9AD8E6E030D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8672F60-3EC2-4BAC-9988-FC6D7DF06974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="4350" windowWidth="26430" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
